--- a/docs/oc-mensuales/desarrollo-y-mantencion-de-software-ti-e-iaas/ene-2025.xlsx
+++ b/docs/oc-mensuales/desarrollo-y-mantencion-de-software-ti-e-iaas/ene-2025.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OC ene-2025" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="OC ene-2025" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -549,7 +549,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -610,7 +610,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -671,7 +671,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -732,7 +732,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -793,7 +793,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -854,7 +854,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -915,7 +915,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -976,7 +976,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1098,7 +1098,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1159,7 +1159,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1281,7 +1281,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1342,7 +1342,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1525,7 +1525,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1647,7 +1647,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1708,7 +1708,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1769,7 +1769,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1830,7 +1830,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -1891,7 +1891,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -1952,7 +1952,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -2013,7 +2013,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -2074,7 +2074,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -2135,7 +2135,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -2257,7 +2257,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -2318,7 +2318,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -2379,7 +2379,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -2440,7 +2440,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -2501,7 +2501,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -2562,7 +2562,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -2623,7 +2623,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -2684,7 +2684,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -2745,7 +2745,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -2867,7 +2867,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -2928,7 +2928,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -2989,7 +2989,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -3050,7 +3050,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -3172,7 +3172,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -3233,7 +3233,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -3294,7 +3294,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -3355,7 +3355,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">

--- a/docs/oc-mensuales/desarrollo-y-mantencion-de-software-ti-e-iaas/ene-2025.xlsx
+++ b/docs/oc-mensuales/desarrollo-y-mantencion-de-software-ti-e-iaas/ene-2025.xlsx
@@ -1035,11 +1035,7 @@
           <t>MUNICIPALIDAD DE PUDAHUEL</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+      <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr">
         <is>
           <t>MEETCARD</t>
@@ -1584,11 +1580,7 @@
           <t>INSTITUTO DE SALUD PUBLICA DE CHILE</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+      <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr">
         <is>
           <t>SOC DE INVESTIGACION Y DESARROLLO KBINNOVA LIMITADA</t>
@@ -1713,7 +1705,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>VICTORIA SpA</t>
+          <t>VICTORIA S.A</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -3035,7 +3027,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">

--- a/docs/oc-mensuales/desarrollo-y-mantencion-de-software-ti-e-iaas/ene-2025.xlsx
+++ b/docs/oc-mensuales/desarrollo-y-mantencion-de-software-ti-e-iaas/ene-2025.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M48"/>
+  <dimension ref="A1:M50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -623,7 +623,11 @@
           <t>76.384.526-5</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr">
         <is>
           <t>USD</t>
@@ -684,7 +688,11 @@
           <t>76.083.145-k</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr">
         <is>
           <t>USD</t>
@@ -867,7 +875,11 @@
           <t>77.077.350-4</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr">
         <is>
           <t>USD</t>
@@ -928,7 +940,11 @@
           <t>76.018.273-7</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr">
         <is>
           <t>USD</t>
@@ -989,7 +1005,11 @@
           <t>77.185.932-1</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1107,7 +1127,11 @@
           <t>76.304.354-1</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1229,7 +1253,11 @@
           <t>76.376.088-k</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L13" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1290,7 +1318,11 @@
           <t>76.286.397-9</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L14" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1364,7 +1396,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>721-2-CM25</t>
+          <t>2735-52-SE25</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1379,7 +1411,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025-01-15</t>
+          <t>2025-01-14</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1389,12 +1421,12 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>61.108.000-k</t>
+          <t>69.255.200-8</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>CAJA DE PREVISION DE LA DEFENSA NACIONAL</t>
+          <t>I MUNICIPALIDAD LO BARNECHEA</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1404,28 +1436,32 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>TRANSACTION LINE CHILE S.A.</t>
+          <t>LUUK SPA</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>76.300.290-K</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr"/>
+          <t>77.363.384-3</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L16" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>17857.78</v>
+        <v>12420.83</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>598-348-CM24</t>
+          <t>721-2-CM25</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1440,7 +1476,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025-01-16</t>
+          <t>2025-01-15</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1450,12 +1486,12 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>61.513.000-1</t>
+          <t>61.108.000-k</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>DIRECCION PREVISION DE CARABINEROS DE CHILE</t>
+          <t>CAJA DE PREVISION DE LA DEFENSA NACIONAL</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1465,12 +1501,12 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Desarrollo Evaluación Control y Asesorías Ltda.</t>
+          <t>TRANSACTION LINE CHILE S.A.</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>78.299.550-2</t>
+          <t>76.300.290-K</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
@@ -1480,13 +1516,13 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>78705.17999999999</v>
+        <v>17857.78</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>654478-12-CM25</t>
+          <t>598-348-CM24</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1511,12 +1547,12 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>61.980.140-7</t>
+          <t>61.513.000-1</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE PREVENCION DEL DELITO</t>
+          <t>DIRECCION PREVISION DE CARABINEROS DE CHILE</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1526,12 +1562,12 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>CONSULTORIA INFORMATICA CUNIX LIMITADA</t>
+          <t>Desarrollo Evaluación Control y Asesorías Ltda.</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>76.304.354-1</t>
+          <t>78.299.550-2</t>
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
@@ -1541,13 +1577,13 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>29385.77</v>
+        <v>78705.17999999999</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>813-104-CM25</t>
+          <t>654478-12-CM25</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1562,49 +1598,57 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025-01-17</t>
+          <t>2025-01-16</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>61.605.000-1</t>
+          <t>61.980.140-7</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>INSTITUTO DE SALUD PUBLICA DE CHILE</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr"/>
+          <t>SUBSECRETARIA DE PREVENCION DEL DELITO</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>SOC DE INVESTIGACION Y DESARROLLO KBINNOVA LIMITADA</t>
+          <t>CONSULTORIA INFORMATICA CUNIX LIMITADA</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>76.098.050-1</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr"/>
+          <t>76.304.354-1</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L19" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>10004.68</v>
+        <v>29385.77</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>731-19-CM25</t>
+          <t>813-104-CM25</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1619,37 +1663,33 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025-01-20</t>
+          <t>2025-01-17</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>61.008.000-6</t>
+          <t>61.605.000-1</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE MENORES</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>INSTITUTO DE SALUD PUBLICA DE CHILE</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr">
         <is>
-          <t>TIVIT CHILE TERCERIZACION DE PROCESOS, SERVICIOS Y TECNOLOGIA SPA</t>
+          <t>SOC DE INVESTIGACION Y DESARROLLO KBINNOVA LIMITADA</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>76.130.712-6</t>
+          <t>76.098.050-1</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
@@ -1659,13 +1699,13 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>196230.22</v>
+        <v>10004.68</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2328-26-CM25</t>
+          <t>731-19-CM25</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1685,32 +1725,32 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>69.220.100-0</t>
+          <t>61.008.000-6</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUERTO MONTT</t>
+          <t>SERVICIO NACIONAL DE MENORES</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>VICTORIA S.A</t>
+          <t>TIVIT CHILE TERCERIZACION DE PROCESOS, SERVICIOS Y TECNOLOGIA SPA</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>76.188.587-1</t>
+          <t>76.130.712-6</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
@@ -1720,13 +1760,13 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>8852.549999999999</v>
+        <v>196230.22</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>1211839-15-CM25</t>
+          <t>2328-26-CM25</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1741,7 +1781,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025-01-21</t>
+          <t>2025-01-20</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1751,43 +1791,47 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>70.856.400-1</t>
+          <t>69.220.100-0</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>CORP MUNIC EDUC SALUD Y ATENCION</t>
+          <t>I MUNICIPALIDAD DE PUERTO MONTT</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>TCHILECOM</t>
+          <t>VICTORIA S.A</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>77.349.120-8</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr"/>
+          <t>76.188.587-1</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L22" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>15782.32</v>
+        <v>8852.549999999999</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>907581-3-CM25</t>
+          <t>1211839-15-CM25</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1802,7 +1846,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025-01-22</t>
+          <t>2025-01-21</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1812,27 +1856,27 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>60.921.000-1</t>
+          <t>70.856.400-1</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE VALPARAISO</t>
+          <t>CORP MUNIC EDUC SALUD Y ATENCION</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>EXE IOT LIMITADA</t>
+          <t>TCHILECOM</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>77.036.438-8</t>
+          <t>77.349.120-8</t>
         </is>
       </c>
       <c r="K23" t="inlineStr"/>
@@ -1842,7 +1886,7 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>33360.89</v>
+        <v>15782.32</v>
       </c>
     </row>
     <row r="24">
@@ -1896,7 +1940,11 @@
           <t>76.304.354-1</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L24" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1909,7 +1957,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2422-66-CM25</t>
+          <t>907581-3-CM25</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1924,53 +1972,57 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025-01-23</t>
+          <t>2025-01-22</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>69.072.100-7</t>
+          <t>60.921.000-1</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUENTE ALTO</t>
+          <t>UNIVERSIDAD DE VALPARAISO</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>MEETCARD</t>
+          <t>EXE IOT LIMITADA</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>76.437.288-3</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr"/>
+          <t>77.036.438-8</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L25" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>25623.66</v>
+        <v>33360.89</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>1314-86-CM24</t>
+          <t>2422-66-CM25</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1990,17 +2042,17 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>60.706.000-2</t>
+          <t>69.072.100-7</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>CORPORACION DE FOMENTO DE LA PRODUCCION</t>
+          <t>I MUNICIPALIDAD DE PUENTE ALTO</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2010,12 +2062,12 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Austranet Ltda</t>
+          <t>MEETCARD</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>76.009.432-3</t>
+          <t>76.437.288-3</t>
         </is>
       </c>
       <c r="K26" t="inlineStr"/>
@@ -2025,13 +2077,13 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>17767.67</v>
+        <v>25623.66</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>1314-85-CM24</t>
+          <t>1314-86-CM24</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2046,7 +2098,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025-01-24</t>
+          <t>2025-01-23</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -2071,12 +2123,12 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>SOCIEDAD PROFESIONAL  VALIO LIMITADA</t>
+          <t>Austranet Ltda</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>77.714.387-5</t>
+          <t>76.009.432-3</t>
         </is>
       </c>
       <c r="K27" t="inlineStr"/>
@@ -2086,13 +2138,13 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>17869.58</v>
+        <v>17767.67</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>520149-4-CM25</t>
+          <t>1020-809-SE24</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2107,22 +2159,22 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025-01-27</t>
+          <t>2025-01-23</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>60.601.000-1</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE RELACIONES EXTERIORES</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2132,28 +2184,32 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>VAB Ingeniería de Software Limitada</t>
+          <t>ABENIS</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>76.090.261-6</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr"/>
+          <t>76.217.169-4</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L28" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>59092.98</v>
+        <v>25111.19</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2675-30-CM25</t>
+          <t>1314-85-CM24</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2168,53 +2224,57 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025-01-27</t>
+          <t>2025-01-24</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>69.080.500-6</t>
+          <t>60.706.000-2</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MOSTAZAL</t>
+          <t>CORPORACION DE FOMENTO DE LA PRODUCCION</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>SOSAFE</t>
+          <t>SOCIEDAD PROFESIONAL  VALIO LIMITADA</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>76.376.088-k</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr"/>
+          <t>77.714.387-5</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L29" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>18937.22</v>
+        <v>17869.58</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2021-1-CM25</t>
+          <t>520149-4-CM25</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2229,7 +2289,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025-01-28</t>
+          <t>2025-01-27</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -2239,12 +2299,12 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>61.101.040-0</t>
+          <t>60.601.000-1</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>ESTADO MAYOR CONJUNTO</t>
+          <t>SUBSECRETARIA DE RELACIONES EXTERIORES</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2254,12 +2314,12 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>TCHILECOM</t>
+          <t>VAB Ingeniería de Software Limitada</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>77.349.120-8</t>
+          <t>76.090.261-6</t>
         </is>
       </c>
       <c r="K30" t="inlineStr"/>
@@ -2269,13 +2329,13 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>16096.26</v>
+        <v>59092.98</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>5416-100-CM25</t>
+          <t>2675-30-CM25</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2290,7 +2350,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025-01-29</t>
+          <t>2025-01-27</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -2300,43 +2360,47 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>70.783.100-6</t>
+          <t>69.080.500-6</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE LA SERENA</t>
+          <t>I MUNICIPALIDAD DE MOSTAZAL</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>SONDA S A</t>
+          <t>SOSAFE</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>83.628.100-4</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr"/>
+          <t>76.376.088-k</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L31" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>12419.93</v>
+        <v>18937.22</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2677-28-CM25</t>
+          <t>2021-1-CM25</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2351,37 +2415,37 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025-01-29</t>
+          <t>2025-01-28</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>69.080.500-6</t>
+          <t>61.101.040-0</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MOSTAZAL</t>
+          <t>ESTADO MAYOR CONJUNTO</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Rayen Salud SpA</t>
+          <t>TCHILECOM</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>77.917.240-6</t>
+          <t>77.349.120-8</t>
         </is>
       </c>
       <c r="K32" t="inlineStr"/>
@@ -2391,13 +2455,13 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>60481.06</v>
+        <v>16096.26</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>1314-9-CM25</t>
+          <t>1233616-16-CM25</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2417,48 +2481,52 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>60.706.000-2</t>
+          <t>61.980.940-8</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>CORPORACION DE FOMENTO DE LA PRODUCCION</t>
+          <t>Servicio Local de Educación Pública Punilla Cordillera</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>NEURONET SOLUCIONES DE INGENIERIA Y TECNOLOGIA S.A.</t>
+          <t>CLARO CHILE S.A.</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>77.077.350-4</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr"/>
+          <t>96.799.250-k</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L33" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>14580.69</v>
+        <v>13532.73</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>1233616-16-CM25</t>
+          <t>5416-100-CM25</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2483,27 +2551,27 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>61.980.940-8</t>
+          <t>70.783.100-6</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Punilla Cordillera</t>
+          <t>UNIVERSIDAD DE LA SERENA</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>CLARO CHILE S.A.</t>
+          <t>SONDA S A</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>96.799.250-k</t>
+          <t>83.628.100-4</t>
         </is>
       </c>
       <c r="K34" t="inlineStr"/>
@@ -2513,13 +2581,13 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>13532.73</v>
+        <v>12419.93</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>5768-21-CM25</t>
+          <t>2677-28-CM25</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2539,32 +2607,32 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>69.080.500-6</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>I MUNICIPALIDAD DE MOSTAZAL</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Inteldata Ltda.</t>
+          <t>Rayen Salud SpA</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>76.414.840-1</t>
+          <t>77.917.240-6</t>
         </is>
       </c>
       <c r="K35" t="inlineStr"/>
@@ -2574,13 +2642,13 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>17633.87</v>
+        <v>60481.06</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>1778-586-CM24</t>
+          <t>1314-9-CM25</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2600,17 +2668,17 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>61.533.000-0</t>
+          <t>60.706.000-2</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>INSTITUTO DE SEGURIDAD LABORAL</t>
+          <t>CORPORACION DE FOMENTO DE LA PRODUCCION</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2620,28 +2688,32 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Kibernum S.A</t>
+          <t>NEURONET SOLUCIONES DE INGENIERIA Y TECNOLOGIA S.A.</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>96.616.770-k</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr"/>
+          <t>77.077.350-4</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L36" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>31119.04</v>
+        <v>14580.69</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>587-928-CM24</t>
+          <t>1415862-5-CM25</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2666,12 +2738,12 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>61.801.000-7</t>
+          <t>61.533.000-0</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DEL MINISTERIO DE LA VIVIENDA Y URBANISMO</t>
+          <t>INSTITUTO DE SEGURIDAD LABORAL</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2681,28 +2753,32 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Tecnología y Servicios Informáticos Advise S.A.</t>
+          <t>LDV SERVICIOS PROFESIONALES COMPUTACIONALES LIMITADA</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>76.186.623-0</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr"/>
+          <t>77.681.168-8</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L37" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>29869.61</v>
+        <v>35221.38</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>1415862-5-CM25</t>
+          <t>5768-21-CM25</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2727,12 +2803,12 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>61.533.000-0</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>INSTITUTO DE SEGURIDAD LABORAL</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2742,12 +2818,12 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>LDV SERVICIOS PROFESIONALES COMPUTACIONALES LIMITADA</t>
+          <t>Inteldata Ltda.</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>77.681.168-8</t>
+          <t>76.414.840-1</t>
         </is>
       </c>
       <c r="K38" t="inlineStr"/>
@@ -2757,13 +2833,13 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>35221.38</v>
+        <v>17633.87</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2268-363-CM24</t>
+          <t>1778-586-CM24</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2778,22 +2854,22 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2025-01-30</t>
+          <t>2025-01-29</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>61.608.700-2</t>
+          <t>61.533.000-0</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>CENTRAL DE ABASTECIMIENTO DEL SISTEMA NACIONAL DE SERVICIO DE SALUD</t>
+          <t>INSTITUTO DE SEGURIDAD LABORAL</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2803,12 +2879,12 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>APIUX TECNOLOGIA SPA</t>
+          <t>Kibernum S.A</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>76.516.485-0</t>
+          <t>96.616.770-k</t>
         </is>
       </c>
       <c r="K39" t="inlineStr"/>
@@ -2818,13 +2894,13 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>611852.64</v>
+        <v>31119.04</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>1876-1-CM25</t>
+          <t>587-928-CM24</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2839,7 +2915,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2025-01-30</t>
+          <t>2025-01-29</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -2849,12 +2925,12 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>61.941.900-6</t>
+          <t>61.801.000-7</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>DEFENSORIA PENAL PUBLICA</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE LA VIVIENDA Y URBANISMO</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -2864,12 +2940,12 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>BROWSE INGENIERIA DE SOFTWARE SOCIEDAD ANONIMA</t>
+          <t>Tecnología y Servicios Informáticos Advise S.A.</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>79.822.840-4</t>
+          <t>76.186.623-0</t>
         </is>
       </c>
       <c r="K40" t="inlineStr"/>
@@ -2879,13 +2955,13 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>58442.05</v>
+        <v>29869.61</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>5251-92-CM25</t>
+          <t>2268-363-CM24</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2905,17 +2981,17 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>70.729.100-1</t>
+          <t>61.608.700-2</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD TECNOLOGICA METROPOLITANA</t>
+          <t>CENTRAL DE ABASTECIMIENTO DEL SISTEMA NACIONAL DE SERVICIO DE SALUD</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -2925,28 +3001,32 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>SECAPPS TECHNOLOGIES SPA</t>
+          <t>APIUX TECNOLOGIA SPA</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>77.660.154-3</t>
-        </is>
-      </c>
-      <c r="K41" t="inlineStr"/>
+          <t>76.516.485-0</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L41" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>32074.94</v>
+        <v>611852.64</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>1602-14-CM25</t>
+          <t>1876-1-CM25</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2961,7 +3041,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2025-01-31</t>
+          <t>2025-01-30</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -2971,12 +3051,12 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>61.104.000-8</t>
+          <t>61.941.900-6</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE AERONAUTICA CIVIL</t>
+          <t>DEFENSORIA PENAL PUBLICA</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -2986,12 +3066,12 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>SOLUCIONES TECNOLÓGICAS COORDENADA SPA</t>
+          <t>BROWSE INGENIERIA DE SOFTWARE SOCIEDAD ANONIMA</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>76.489.853-2</t>
+          <t>79.822.840-4</t>
         </is>
       </c>
       <c r="K42" t="inlineStr"/>
@@ -3001,13 +3081,13 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>49037.22</v>
+        <v>58442.05</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>3178-4043-CM24</t>
+          <t>5251-92-CM25</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3022,53 +3102,57 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2025-01-31</t>
+          <t>2025-01-30</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>61.102.025-2</t>
+          <t>70.729.100-1</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+          <t>UNIVERSIDAD TECNOLOGICA METROPOLITANA</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>BARDANE SPA</t>
+          <t>SECAPPS TECHNOLOGIES SPA</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>77.205.722-9</t>
-        </is>
-      </c>
-      <c r="K43" t="inlineStr"/>
+          <t>77.660.154-3</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L43" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>11780.52</v>
+        <v>32074.94</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>1607-237-CM24</t>
+          <t>1602-12-CM25</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3093,12 +3177,12 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>61.509.000-k</t>
+          <t>61.104.000-8</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>SUPERINTENDENCIA DE SEGURIDAD SOCIAL</t>
+          <t>DIRECCION GENERAL DE AERONAUTICA CIVIL</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -3108,12 +3192,12 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>Tecnología y Servicios Informáticos Advise S.A.</t>
+          <t>VIA 56 S A</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>76.186.623-0</t>
+          <t>96.928.990-3</t>
         </is>
       </c>
       <c r="K44" t="inlineStr"/>
@@ -3123,13 +3207,13 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>12463.96</v>
+        <v>27148.89</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>587-19-CM25</t>
+          <t>587-20-CM25</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3169,28 +3253,32 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>ENVISION INVERSIONES LIMITADA</t>
+          <t>CONSULTORIA INFORMATICA CUNIX LIMITADA</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>76.693.295-9</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr"/>
+          <t>76.304.354-1</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L45" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>31540.7</v>
+        <v>39381.57</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>587-20-CM25</t>
+          <t>1602-14-CM25</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3215,12 +3303,12 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>61.801.000-7</t>
+          <t>61.104.000-8</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DEL MINISTERIO DE LA VIVIENDA Y URBANISMO</t>
+          <t>DIRECCION GENERAL DE AERONAUTICA CIVIL</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -3230,12 +3318,12 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>CONSULTORIA INFORMATICA CUNIX LIMITADA</t>
+          <t>SOLUCIONES TECNOLÓGICAS COORDENADA SPA</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>76.304.354-1</t>
+          <t>76.489.853-2</t>
         </is>
       </c>
       <c r="K46" t="inlineStr"/>
@@ -3245,13 +3333,13 @@
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>39381.57</v>
+        <v>49037.22</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>1602-12-CM25</t>
+          <t>1607-237-CM24</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3276,12 +3364,12 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>61.104.000-8</t>
+          <t>61.509.000-k</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE AERONAUTICA CIVIL</t>
+          <t>SUPERINTENDENCIA DE SEGURIDAD SOCIAL</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -3291,12 +3379,12 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>VIA 56 S A</t>
+          <t>Tecnología y Servicios Informáticos Advise S.A.</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>96.928.990-3</t>
+          <t>76.186.623-0</t>
         </is>
       </c>
       <c r="K47" t="inlineStr"/>
@@ -3306,13 +3394,13 @@
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>27148.89</v>
+        <v>12463.96</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>1057554-51-CM25</t>
+          <t>3178-4043-CM24</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3337,27 +3425,27 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>61.602.054-4</t>
+          <t>61.102.025-2</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL CARLOS VAN BUREN</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>BROWSE INGENIERIA DE SOFTWARE SOCIEDAD ANONIMA</t>
+          <t>BARDANE SPA</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>79.822.840-4</t>
+          <t>77.205.722-9</t>
         </is>
       </c>
       <c r="K48" t="inlineStr"/>
@@ -3367,6 +3455,128 @@
         </is>
       </c>
       <c r="M48" s="2" t="n">
+        <v>11780.52</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>587-19-CM25</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>ene-2025</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>2025-01-31</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>61.801.000-7</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>SUBSECRETARIA DEL MINISTERIO DE LA VIVIENDA Y URBANISMO</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>ENVISION INVERSIONES LIMITADA</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>76.693.295-9</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="n">
+        <v>31540.7</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>1057554-51-CM25</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>ene-2025</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>2025-01-31</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>61.602.054-4</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL CARLOS VAN BUREN</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>BROWSE INGENIERIA DE SOFTWARE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>79.822.840-4</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="n">
         <v>14715.9</v>
       </c>
     </row>

--- a/docs/oc-mensuales/desarrollo-y-mantencion-de-software-ti-e-iaas/ene-2025.xlsx
+++ b/docs/oc-mensuales/desarrollo-y-mantencion-de-software-ti-e-iaas/ene-2025.xlsx
@@ -2887,7 +2887,11 @@
           <t>96.616.770-k</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L39" t="inlineStr">
         <is>
           <t>USD</t>

--- a/docs/oc-mensuales/desarrollo-y-mantencion-de-software-ti-e-iaas/ene-2025.xlsx
+++ b/docs/oc-mensuales/desarrollo-y-mantencion-de-software-ti-e-iaas/ene-2025.xlsx
@@ -1055,7 +1055,11 @@
           <t>MUNICIPALIDAD DE PUDAHUEL</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr"/>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="I10" t="inlineStr">
         <is>
           <t>MEETCARD</t>
@@ -1681,7 +1685,11 @@
           <t>INSTITUTO DE SALUD PUBLICA DE CHILE</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr"/>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="I20" t="inlineStr">
         <is>
           <t>SOC DE INVESTIGACION Y DESARROLLO KBINNOVA LIMITADA</t>
@@ -1806,7 +1814,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>VICTORIA S.A</t>
+          <t>VICTORIA SpA</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -3424,7 +3432,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
